--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.32408465340226</v>
+        <v>10.29016375617787</v>
       </c>
       <c r="D2" t="n">
-        <v>57.00616281809441</v>
+        <v>9.263501457940341</v>
       </c>
       <c r="E2" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.10031967944761</v>
+        <v>5.053801947910237</v>
       </c>
       <c r="D3" t="n">
-        <v>25.22896296393676</v>
+        <v>4.099706481639723</v>
       </c>
       <c r="E3" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.81474865806805</v>
+        <v>7.119896656936058</v>
       </c>
       <c r="D4" t="n">
-        <v>37.22823049074719</v>
+        <v>6.049587454746418</v>
       </c>
       <c r="E4" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.03130754150702</v>
+        <v>5.042587475494892</v>
       </c>
       <c r="D5" t="n">
-        <v>13.12440474840669</v>
+        <v>2.132715771616087</v>
       </c>
       <c r="E5" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.72593221567504</v>
+        <v>5.155463985047193</v>
       </c>
       <c r="D6" t="n">
-        <v>32.3416125665863</v>
+        <v>5.255512042070274</v>
       </c>
       <c r="E6" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F6" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.74532513568436</v>
+        <v>4.183615334548709</v>
       </c>
       <c r="D7" t="n">
-        <v>19.82905807250389</v>
+        <v>3.222221936781882</v>
       </c>
       <c r="E7" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F7" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.21810587941468</v>
+        <v>7.510442205404885</v>
       </c>
       <c r="D8" t="n">
-        <v>25.52852885826608</v>
+        <v>4.148385939468239</v>
       </c>
       <c r="E8" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.77632903283107</v>
+        <v>4.51365346783505</v>
       </c>
       <c r="D9" t="n">
-        <v>26.70758763622196</v>
+        <v>4.339982990886069</v>
       </c>
       <c r="E9" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F9" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.8305128776203</v>
+        <v>3.059958342613299</v>
       </c>
       <c r="D10" t="n">
-        <v>18.84265208593967</v>
+        <v>3.061930963965197</v>
       </c>
       <c r="E10" t="n">
-        <v>12.66860772219419</v>
+        <v>2.058648754856555</v>
       </c>
       <c r="F10" t="n">
-        <v>12.1613828701256</v>
+        <v>1.97622471639541</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
